--- a/artfynd/A 27575-2025 artfynd.xlsx
+++ b/artfynd/A 27575-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132345513</v>
+        <v>7021045</v>
       </c>
       <c r="B2" t="n">
-        <v>58136</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vallhall, Hjd</t>
+          <t>Björnsjöberget, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>416884</v>
+        <v>416945</v>
       </c>
       <c r="R2" t="n">
-        <v>6971301</v>
+        <v>6971302</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2013-10-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2013-10-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132346107</v>
+        <v>132346110</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>78776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -874,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132346738</v>
+        <v>132346754</v>
       </c>
       <c r="B4" t="n">
-        <v>78363</v>
+        <v>78776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -971,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132346091</v>
+        <v>132346107</v>
       </c>
       <c r="B5" t="n">
-        <v>79949</v>
+        <v>79130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,32 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132346110</v>
+        <v>132345292</v>
       </c>
       <c r="B6" t="n">
-        <v>78762</v>
+        <v>80499</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416818</v>
+        <v>416903</v>
       </c>
       <c r="R6" t="n">
-        <v>6971298</v>
+        <v>6971333</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132346754</v>
+        <v>132346103</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>78377</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1175,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416724</v>
+        <v>416818</v>
       </c>
       <c r="R7" t="n">
-        <v>6971271</v>
+        <v>6971298</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132346103</v>
+        <v>132346738</v>
       </c>
       <c r="B8" t="n">
-        <v>78363</v>
+        <v>78377</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416818</v>
+        <v>416724</v>
       </c>
       <c r="R8" t="n">
-        <v>6971298</v>
+        <v>6971271</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,6 +1355,205 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132345513</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vallhall, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>416884</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6971301</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132346091</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vallhall, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>416818</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6971298</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27575-2025 artfynd.xlsx
+++ b/artfynd/A 27575-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7021045</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132346110</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132346754</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132346107</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132345292</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132346103</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132346738</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132345513</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,8 +1599,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132346091</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27575-2025 artfynd.xlsx
+++ b/artfynd/A 27575-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7021045</v>
+        <v>135784672</v>
       </c>
       <c r="B2" t="n">
-        <v>78993</v>
+        <v>97511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björnsjöberget, Hjd</t>
+          <t>Lövdalen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>416945</v>
+        <v>416868</v>
       </c>
       <c r="R2" t="n">
-        <v>6971302</v>
+        <v>6971209</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-10-23</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-10-23</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,31 +765,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7021045</t>
+          <t>https://artportalen.se/Sighting/135784672</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132346110</v>
+        <v>7021045</v>
       </c>
       <c r="B3" t="n">
-        <v>78776</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vallhall, Hjd</t>
+          <t>Björnsjöberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416818</v>
+        <v>416945</v>
       </c>
       <c r="R3" t="n">
-        <v>6971298</v>
+        <v>6971302</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2013-10-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2013-10-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,27 +867,31 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132346110</t>
+          <t>https://artportalen.se/Sighting/7021045</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132346754</v>
+        <v>135784673</v>
       </c>
       <c r="B4" t="n">
-        <v>78776</v>
+        <v>79107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,34 +899,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vallhall, Hjd</t>
+          <t>Lövdalen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416724</v>
+        <v>416871</v>
       </c>
       <c r="R4" t="n">
-        <v>6971271</v>
+        <v>6971216</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,27 +973,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132346754</t>
+          <t>https://artportalen.se/Sighting/135784673</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132346107</v>
+        <v>135784679</v>
       </c>
       <c r="B5" t="n">
-        <v>79130</v>
+        <v>89290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,34 +1001,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vallhall, Hjd</t>
+          <t>Lövdalen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416818</v>
+        <v>416697</v>
       </c>
       <c r="R5" t="n">
-        <v>6971298</v>
+        <v>6971324</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,49 +1075,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132346107</t>
+          <t>https://artportalen.se/Sighting/135784679</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132345292</v>
+        <v>132346110</v>
       </c>
       <c r="B6" t="n">
-        <v>80499</v>
+        <v>78776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>416903</v>
+        <v>416818</v>
       </c>
       <c r="R6" t="n">
-        <v>6971333</v>
+        <v>6971298</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,16 +1188,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132345292</t>
+          <t>https://artportalen.se/Sighting/132346110</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132346103</v>
+        <v>132346754</v>
       </c>
       <c r="B7" t="n">
-        <v>78377</v>
+        <v>78776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,21 +1205,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416818</v>
+        <v>416724</v>
       </c>
       <c r="R7" t="n">
-        <v>6971298</v>
+        <v>6971271</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,16 +1290,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132346103</t>
+          <t>https://artportalen.se/Sighting/132346754</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132346738</v>
+        <v>135784677</v>
       </c>
       <c r="B8" t="n">
-        <v>78377</v>
+        <v>78844</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,34 +1307,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vallhall, Hjd</t>
+          <t>Lövdalen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416724</v>
+        <v>416860</v>
       </c>
       <c r="R8" t="n">
-        <v>6971271</v>
+        <v>6971220</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,27 +1381,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132346738</t>
+          <t>https://artportalen.se/Sighting/135784677</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132345513</v>
+        <v>132346107</v>
       </c>
       <c r="B9" t="n">
-        <v>58136</v>
+        <v>79130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,42 +1409,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vallhall, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416884</v>
+        <v>416818</v>
       </c>
       <c r="R9" t="n">
-        <v>6971301</v>
+        <v>6971298</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1499,16 +1494,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132345513</t>
+          <t>https://artportalen.se/Sighting/132346107</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132346091</v>
+        <v>135784674</v>
       </c>
       <c r="B10" t="n">
-        <v>79963</v>
+        <v>80060</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,34 +1511,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vallhall, Hjd</t>
+          <t>Lövdalen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416818</v>
+        <v>416864</v>
       </c>
       <c r="R10" t="n">
-        <v>6971298</v>
+        <v>6971226</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1570,12 +1565,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,18 +1585,839 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135784674</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132345292</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80499</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vallhall, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>416903</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6971333</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132345292</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135784676</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80567</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>416846</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6971230</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784676</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132346103</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vallhall, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>416818</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6971298</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132346103</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132346738</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vallhall, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>416724</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6971271</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132346738</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135784680</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57801</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>416845</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6971269</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784680</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132345513</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vallhall, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>416884</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6971301</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132345513</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132346091</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vallhall, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>416818</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6971298</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/132346091</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135784678</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>416860</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6971221</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784678</t>
         </is>
       </c>
     </row>
@@ -1616,6 +2432,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27575-2025 artfynd.xlsx
+++ b/artfynd/A 27575-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784672</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784679</v>
       </c>
       <c r="B5" t="n">
-        <v>89290</v>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27575-2025 artfynd.xlsx
+++ b/artfynd/A 27575-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784672</v>
       </c>
       <c r="B2" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135784673</v>
       </c>
       <c r="B4" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784679</v>
       </c>
       <c r="B5" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>135784677</v>
       </c>
       <c r="B8" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135784674</v>
       </c>
       <c r="B10" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135784676</v>
       </c>
       <c r="B12" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>135784680</v>
       </c>
       <c r="B15" t="n">
-        <v>57801</v>
+        <v>57803</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>135784678</v>
       </c>
       <c r="B18" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 27575-2025 artfynd.xlsx
+++ b/artfynd/A 27575-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784672</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135784673</v>
       </c>
       <c r="B4" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784679</v>
       </c>
       <c r="B5" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>135784677</v>
       </c>
       <c r="B8" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135784674</v>
       </c>
       <c r="B10" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135784676</v>
       </c>
       <c r="B12" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>135784678</v>
       </c>
       <c r="B18" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 27575-2025 artfynd.xlsx
+++ b/artfynd/A 27575-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784672</v>
       </c>
       <c r="B2" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784679</v>
       </c>
       <c r="B5" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27575-2025 artfynd.xlsx
+++ b/artfynd/A 27575-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784672</v>
       </c>
       <c r="B2" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135784673</v>
       </c>
       <c r="B4" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784679</v>
       </c>
       <c r="B5" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>135784677</v>
       </c>
       <c r="B8" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135784674</v>
       </c>
       <c r="B10" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135784676</v>
       </c>
       <c r="B12" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>135784680</v>
       </c>
       <c r="B15" t="n">
-        <v>57803</v>
+        <v>57804</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>135784678</v>
       </c>
       <c r="B18" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 27575-2025 artfynd.xlsx
+++ b/artfynd/A 27575-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784672</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135784673</v>
       </c>
       <c r="B4" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784679</v>
       </c>
       <c r="B5" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>135784677</v>
       </c>
       <c r="B8" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135784674</v>
       </c>
       <c r="B10" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135784676</v>
       </c>
       <c r="B12" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>135784680</v>
       </c>
       <c r="B15" t="n">
-        <v>57804</v>
+        <v>57808</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>135784678</v>
       </c>
       <c r="B18" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 27575-2025 artfynd.xlsx
+++ b/artfynd/A 27575-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784672</v>
       </c>
       <c r="B2" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135784673</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784679</v>
       </c>
       <c r="B5" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>135784677</v>
       </c>
       <c r="B8" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135784674</v>
       </c>
       <c r="B10" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135784676</v>
       </c>
       <c r="B12" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>135784680</v>
       </c>
       <c r="B15" t="n">
-        <v>57808</v>
+        <v>57809</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>135784678</v>
       </c>
       <c r="B18" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 27575-2025 artfynd.xlsx
+++ b/artfynd/A 27575-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784672</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135784673</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784679</v>
       </c>
       <c r="B5" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>135784677</v>
       </c>
       <c r="B8" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135784674</v>
       </c>
       <c r="B10" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135784676</v>
       </c>
       <c r="B12" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>135784678</v>
       </c>
       <c r="B18" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 27575-2025 artfynd.xlsx
+++ b/artfynd/A 27575-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784672</v>
       </c>
       <c r="B2" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135784673</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784679</v>
       </c>
       <c r="B5" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>135784677</v>
       </c>
       <c r="B8" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135784674</v>
       </c>
       <c r="B10" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135784676</v>
       </c>
       <c r="B12" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>135784680</v>
       </c>
       <c r="B15" t="n">
-        <v>57809</v>
+        <v>57814</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>135784678</v>
       </c>
       <c r="B18" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 27575-2025 artfynd.xlsx
+++ b/artfynd/A 27575-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784672</v>
       </c>
       <c r="B2" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784679</v>
       </c>
       <c r="B5" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
